--- a/Assets/Excel/技能配置表.xlsx
+++ b/Assets/Excel/技能配置表.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="76" uniqueCount="51">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="82" uniqueCount="52">
   <si>
     <t>f_id</t>
   </si>
@@ -129,10 +129,12 @@
   </si>
   <si>
     <t>技能伤害属性类型
+0：无
 1：火
 2：冰
 3：物理
-4：量子</t>
+4：量子
+5：风</t>
   </si>
   <si>
     <t>伤害类型
@@ -190,6 +192,9 @@
   </si>
   <si>
     <t>NormalAttack</t>
+  </si>
+  <si>
+    <t>10001,10003,10004</t>
   </si>
   <si>
     <t>战士战技</t>
@@ -862,7 +867,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -878,7 +883,22 @@
     <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1210,7 +1230,7 @@
     <col min="13" max="13" width="16" customWidth="1"/>
     <col min="14" max="14" width="14.625" customWidth="1"/>
     <col min="15" max="15" width="16" customWidth="1"/>
-    <col min="16" max="16" width="15.375" customWidth="1"/>
+    <col min="16" max="16" width="20.1083333333333" style="5" customWidth="1"/>
     <col min="17" max="17" width="11.5" customWidth="1"/>
   </cols>
   <sheetData>
@@ -1260,7 +1280,7 @@
       <c r="O1" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="P1" s="1" t="s">
+      <c r="P1" s="6" t="s">
         <v>15</v>
       </c>
       <c r="Q1" s="1" t="s">
@@ -1313,7 +1333,7 @@
       <c r="O2" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="P2" s="1" t="s">
+      <c r="P2" s="6" t="s">
         <v>18</v>
       </c>
       <c r="Q2" s="1" t="s">
@@ -1324,8 +1344,9 @@
       <c r="A3" s="1" t="s">
         <v>19</v>
       </c>
+      <c r="P3" s="6"/>
     </row>
-    <row r="4" s="1" customFormat="1" ht="212" customHeight="1" spans="1:17">
+    <row r="4" s="1" customFormat="1" ht="118" customHeight="1" spans="1:17">
       <c r="A4" s="1" t="s">
         <v>20</v>
       </c>
@@ -1335,43 +1356,43 @@
       <c r="C4" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="D4" s="5" t="s">
+      <c r="D4" s="7" t="s">
         <v>23</v>
       </c>
-      <c r="E4" s="5" t="s">
+      <c r="E4" s="7" t="s">
         <v>24</v>
       </c>
-      <c r="F4" s="5" t="s">
+      <c r="F4" s="7" t="s">
         <v>25</v>
       </c>
-      <c r="G4" s="5" t="s">
+      <c r="G4" s="7" t="s">
         <v>26</v>
       </c>
-      <c r="H4" s="5" t="s">
+      <c r="H4" s="7" t="s">
         <v>27</v>
       </c>
-      <c r="I4" s="5" t="s">
+      <c r="I4" s="7" t="s">
         <v>28</v>
       </c>
-      <c r="J4" s="5" t="s">
+      <c r="J4" s="7" t="s">
         <v>29</v>
       </c>
-      <c r="K4" s="5" t="s">
+      <c r="K4" s="7" t="s">
         <v>30</v>
       </c>
-      <c r="L4" s="5" t="s">
+      <c r="L4" s="7" t="s">
         <v>31</v>
       </c>
-      <c r="M4" s="5" t="s">
+      <c r="M4" s="7" t="s">
         <v>32</v>
       </c>
-      <c r="N4" s="5" t="s">
+      <c r="N4" s="7" t="s">
         <v>33</v>
       </c>
       <c r="O4" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="P4" s="1" t="s">
+      <c r="P4" s="6" t="s">
         <v>35</v>
       </c>
       <c r="Q4" s="1" t="s">
@@ -1424,8 +1445,8 @@
       <c r="O5" s="2" t="s">
         <v>39</v>
       </c>
-      <c r="P5" s="2">
-        <v>10001</v>
+      <c r="P5" s="8" t="s">
+        <v>40</v>
       </c>
     </row>
     <row r="6" s="2" customFormat="1" ht="28" customHeight="1" spans="1:17">
@@ -1433,7 +1454,7 @@
         <v>11</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="C6" s="2" t="s">
         <v>38</v>
@@ -1472,10 +1493,10 @@
         <v>0</v>
       </c>
       <c r="O6" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="P6" s="2">
-        <v>10001</v>
+        <v>42</v>
+      </c>
+      <c r="P6" s="8" t="s">
+        <v>40</v>
       </c>
     </row>
     <row r="7" s="2" customFormat="1" ht="30" customHeight="1" spans="1:17">
@@ -1483,7 +1504,7 @@
         <v>12</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="C7" s="2" t="s">
         <v>38</v>
@@ -1522,10 +1543,10 @@
         <v>0</v>
       </c>
       <c r="O7" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="P7" s="2">
-        <v>10001</v>
+        <v>44</v>
+      </c>
+      <c r="P7" s="8" t="s">
+        <v>40</v>
       </c>
     </row>
     <row r="8" s="3" customFormat="1" ht="27" customHeight="1" spans="1:17">
@@ -1533,10 +1554,10 @@
         <v>20</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="D8" s="3">
         <v>1</v>
@@ -1574,8 +1595,8 @@
       <c r="O8" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="P8" s="3">
-        <v>10001</v>
+      <c r="P8" s="9" t="s">
+        <v>40</v>
       </c>
     </row>
     <row r="9" s="3" customFormat="1" ht="27" customHeight="1" spans="1:17">
@@ -1583,10 +1604,10 @@
         <v>21</v>
       </c>
       <c r="B9" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="C9" s="3" t="s">
         <v>46</v>
-      </c>
-      <c r="C9" s="3" t="s">
-        <v>45</v>
       </c>
       <c r="D9" s="3">
         <v>2</v>
@@ -1622,10 +1643,10 @@
         <v>0</v>
       </c>
       <c r="O9" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="P9" s="3">
-        <v>10001</v>
+        <v>42</v>
+      </c>
+      <c r="P9" s="9" t="s">
+        <v>40</v>
       </c>
     </row>
     <row r="10" s="3" customFormat="1" ht="27" customHeight="1" spans="1:17">
@@ -1633,10 +1654,10 @@
         <v>22</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="D10" s="3">
         <v>1</v>
@@ -1672,10 +1693,10 @@
         <v>0</v>
       </c>
       <c r="O10" s="3" t="s">
-        <v>43</v>
-      </c>
-      <c r="P10" s="3">
-        <v>10001</v>
+        <v>44</v>
+      </c>
+      <c r="P10" s="9" t="s">
+        <v>40</v>
       </c>
     </row>
     <row r="11" s="4" customFormat="1" ht="27" customHeight="1" spans="1:17">
@@ -1683,7 +1704,7 @@
         <v>101</v>
       </c>
       <c r="B11" s="4" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="C11" s="4" t="s">
         <v>38</v>
@@ -1722,9 +1743,9 @@
         <v>0</v>
       </c>
       <c r="O11" s="4" t="s">
-        <v>49</v>
-      </c>
-      <c r="P11" s="4">
+        <v>50</v>
+      </c>
+      <c r="P11" s="10">
         <v>20001</v>
       </c>
       <c r="Q11" s="4">
@@ -1736,10 +1757,10 @@
         <v>102</v>
       </c>
       <c r="B12" s="4" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="C12" s="4" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="D12" s="4">
         <v>1</v>
@@ -1775,9 +1796,9 @@
         <v>0</v>
       </c>
       <c r="O12" s="4" t="s">
-        <v>49</v>
-      </c>
-      <c r="P12" s="4">
+        <v>50</v>
+      </c>
+      <c r="P12" s="10">
         <v>20001</v>
       </c>
       <c r="Q12" s="4">

--- a/Assets/Excel/技能配置表.xlsx
+++ b/Assets/Excel/技能配置表.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="82" uniqueCount="52">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="103" uniqueCount="73">
   <si>
     <t>f_id</t>
   </si>
@@ -153,18 +153,10 @@
   </si>
   <si>
     <t>技能动画类型
-0：无
-1：待机
-2：奔跑
-3：预备普攻
-4：普攻
-5：预备战技
-6：战技
-7：预备终结技
-8：终结技
-9：受击
-10：死亡
-11：重生
+0：无、1：待机、2：奔跑
+3：预备普攻、4：普攻、5：预备战技
+6：战技、7：预备终结技、8：终结技
+9：受击、10：死亡、11：重生
 12：怪物通用攻击</t>
   </si>
   <si>
@@ -182,7 +174,7 @@
     <t>技能Buff效果ID</t>
   </si>
   <si>
-    <t>伤害时间</t>
+    <t>触发时间</t>
   </si>
   <si>
     <t>战士普攻</t>
@@ -194,7 +186,7 @@
     <t>NormalAttack</t>
   </si>
   <si>
-    <t>10001,10003,10004</t>
+    <t>101</t>
   </si>
   <si>
     <t>战士战技</t>
@@ -203,31 +195,94 @@
     <t>BattleAttack</t>
   </si>
   <si>
+    <t>111</t>
+  </si>
+  <si>
     <t>战士终结技</t>
   </si>
   <si>
     <t>UltimateAttack</t>
   </si>
   <si>
+    <t>121</t>
+  </si>
+  <si>
+    <t>0.16,0.39,0.58,0.64,0.79,0.81</t>
+  </si>
+  <si>
     <t>法师普攻</t>
   </si>
   <si>
     <t>造成100%攻击力的冰属性伤害</t>
   </si>
   <si>
+    <t>201</t>
+  </si>
+  <si>
+    <t>0.29</t>
+  </si>
+  <si>
     <t>法师战技</t>
   </si>
   <si>
+    <t>211</t>
+  </si>
+  <si>
+    <t>1.52</t>
+  </si>
+  <si>
     <t>法师终结技</t>
   </si>
   <si>
+    <t>221</t>
+  </si>
+  <si>
+    <t>0.46,1.1,1.3,1.5,1.7,1.9</t>
+  </si>
+  <si>
+    <t>牧师普攻</t>
+  </si>
+  <si>
+    <t>造成100%攻击力的风属性伤害</t>
+  </si>
+  <si>
+    <t>301</t>
+  </si>
+  <si>
+    <t>0.04,0.08,0.22,0.37</t>
+  </si>
+  <si>
+    <t>牧师战技</t>
+  </si>
+  <si>
+    <t>311</t>
+  </si>
+  <si>
+    <t>0.05</t>
+  </si>
+  <si>
+    <t>牧师终结技</t>
+  </si>
+  <si>
+    <t>321</t>
+  </si>
+  <si>
+    <t>0.3,0.53,0.81,1.23,1.5</t>
+  </si>
+  <si>
     <t>史莱姆攻击</t>
   </si>
   <si>
     <t>Attack</t>
   </si>
   <si>
+    <t>1011</t>
+  </si>
+  <si>
     <t>甲壳虫攻击</t>
+  </si>
+  <si>
+    <t>1021</t>
   </si>
 </sst>
 </file>
@@ -954,6 +1009,11 @@
     <cellStyle name="60% - 强调文字颜色 6" xfId="48" builtinId="52"/>
   </cellStyles>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
+  <colors>
+    <mruColors>
+      <color rgb="002A4CA2"/>
+    </mruColors>
+  </colors>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
@@ -1212,7 +1272,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:Q12"/>
+  <dimension ref="A1:Q15"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col min="1" max="1" width="14.875" customWidth="1"/>
@@ -1226,12 +1286,12 @@
     <col min="9" max="9" width="18.75" customWidth="1"/>
     <col min="10" max="10" width="13.75" customWidth="1"/>
     <col min="11" max="11" width="18.75" customWidth="1"/>
-    <col min="12" max="12" width="21.5" customWidth="1"/>
+    <col min="12" max="12" width="32.8166666666667" customWidth="1"/>
     <col min="13" max="13" width="16" customWidth="1"/>
     <col min="14" max="14" width="14.625" customWidth="1"/>
     <col min="15" max="15" width="16" customWidth="1"/>
     <col min="16" max="16" width="20.1083333333333" style="5" customWidth="1"/>
-    <col min="17" max="17" width="11.5" customWidth="1"/>
+    <col min="17" max="17" width="25.3166666666667" style="5" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" s="1" customFormat="1" ht="27" customHeight="1" spans="1:17">
@@ -1283,7 +1343,7 @@
       <c r="P1" s="6" t="s">
         <v>15</v>
       </c>
-      <c r="Q1" s="1" t="s">
+      <c r="Q1" s="6" t="s">
         <v>16</v>
       </c>
     </row>
@@ -1336,7 +1396,7 @@
       <c r="P2" s="6" t="s">
         <v>18</v>
       </c>
-      <c r="Q2" s="1" t="s">
+      <c r="Q2" s="6" t="s">
         <v>18</v>
       </c>
     </row>
@@ -1345,8 +1405,9 @@
         <v>19</v>
       </c>
       <c r="P3" s="6"/>
+      <c r="Q3" s="6"/>
     </row>
-    <row r="4" s="1" customFormat="1" ht="118" customHeight="1" spans="1:17">
+    <row r="4" s="1" customFormat="1" ht="94.5" spans="1:17">
       <c r="A4" s="1" t="s">
         <v>20</v>
       </c>
@@ -1395,11 +1456,11 @@
       <c r="P4" s="6" t="s">
         <v>35</v>
       </c>
-      <c r="Q4" s="1" t="s">
+      <c r="Q4" s="6" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="5" s="2" customFormat="1" ht="34" customHeight="1" spans="1:17">
+    <row r="5" s="2" customFormat="1" ht="48" customHeight="1" spans="1:17">
       <c r="A5" s="2">
         <v>10</v>
       </c>
@@ -1448,8 +1509,11 @@
       <c r="P5" s="8" t="s">
         <v>40</v>
       </c>
+      <c r="Q5" s="8">
+        <v>0.2</v>
+      </c>
     </row>
-    <row r="6" s="2" customFormat="1" ht="28" customHeight="1" spans="1:17">
+    <row r="6" s="2" customFormat="1" ht="43" customHeight="1" spans="1:17">
       <c r="A6" s="2">
         <v>11</v>
       </c>
@@ -1496,15 +1560,18 @@
         <v>42</v>
       </c>
       <c r="P6" s="8" t="s">
-        <v>40</v>
+        <v>43</v>
+      </c>
+      <c r="Q6" s="8">
+        <v>0.1</v>
       </c>
     </row>
-    <row r="7" s="2" customFormat="1" ht="30" customHeight="1" spans="1:17">
+    <row r="7" s="2" customFormat="1" ht="56" customHeight="1" spans="1:17">
       <c r="A7" s="2">
         <v>12</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="C7" s="2" t="s">
         <v>38</v>
@@ -1543,21 +1610,24 @@
         <v>0</v>
       </c>
       <c r="O7" s="2" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="P7" s="8" t="s">
-        <v>40</v>
+        <v>46</v>
+      </c>
+      <c r="Q7" s="8" t="s">
+        <v>47</v>
       </c>
     </row>
-    <row r="8" s="3" customFormat="1" ht="27" customHeight="1" spans="1:17">
+    <row r="8" s="3" customFormat="1" ht="38" customHeight="1" spans="1:17">
       <c r="A8" s="3">
         <v>20</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="D8" s="3">
         <v>1</v>
@@ -1596,18 +1666,21 @@
         <v>39</v>
       </c>
       <c r="P8" s="9" t="s">
-        <v>40</v>
+        <v>50</v>
+      </c>
+      <c r="Q8" s="9" t="s">
+        <v>51</v>
       </c>
     </row>
-    <row r="9" s="3" customFormat="1" ht="27" customHeight="1" spans="1:17">
+    <row r="9" s="3" customFormat="1" ht="35" customHeight="1" spans="1:17">
       <c r="A9" s="3">
         <v>21</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>47</v>
+        <v>52</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="D9" s="3">
         <v>2</v>
@@ -1646,18 +1719,21 @@
         <v>42</v>
       </c>
       <c r="P9" s="9" t="s">
-        <v>40</v>
+        <v>53</v>
+      </c>
+      <c r="Q9" s="9" t="s">
+        <v>54</v>
       </c>
     </row>
-    <row r="10" s="3" customFormat="1" ht="27" customHeight="1" spans="1:17">
+    <row r="10" s="3" customFormat="1" ht="35" customHeight="1" spans="1:17">
       <c r="A10" s="3">
         <v>22</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>48</v>
+        <v>55</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="D10" s="3">
         <v>1</v>
@@ -1693,115 +1769,277 @@
         <v>0</v>
       </c>
       <c r="O10" s="3" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="P10" s="9" t="s">
-        <v>40</v>
+        <v>56</v>
+      </c>
+      <c r="Q10" s="9" t="s">
+        <v>57</v>
       </c>
     </row>
-    <row r="11" s="4" customFormat="1" ht="27" customHeight="1" spans="1:17">
-      <c r="A11" s="4">
+    <row r="11" s="2" customFormat="1" ht="27" customHeight="1" spans="1:17">
+      <c r="A11" s="2">
+        <v>30</v>
+      </c>
+      <c r="B11" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="C11" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="D11" s="2">
+        <v>1</v>
+      </c>
+      <c r="E11" s="2">
+        <v>1</v>
+      </c>
+      <c r="F11" s="2">
+        <v>2</v>
+      </c>
+      <c r="G11" s="2">
+        <v>10</v>
+      </c>
+      <c r="H11" s="2">
+        <v>-1</v>
+      </c>
+      <c r="I11" s="2">
+        <v>5</v>
+      </c>
+      <c r="J11" s="2">
+        <v>0</v>
+      </c>
+      <c r="K11" s="2">
+        <v>0</v>
+      </c>
+      <c r="L11" s="2">
+        <v>4</v>
+      </c>
+      <c r="M11" s="2">
+        <v>10</v>
+      </c>
+      <c r="N11" s="2">
+        <v>0</v>
+      </c>
+      <c r="O11" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="P11" s="8" t="s">
+        <v>60</v>
+      </c>
+      <c r="Q11" s="8" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="12" s="2" customFormat="1" ht="27" customHeight="1" spans="1:17">
+      <c r="A12" s="2">
+        <v>31</v>
+      </c>
+      <c r="B12" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="C12" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="D12" s="2">
+        <v>1</v>
+      </c>
+      <c r="E12" s="2">
+        <v>2</v>
+      </c>
+      <c r="F12" s="2">
+        <v>1</v>
+      </c>
+      <c r="G12" s="2">
+        <v>30</v>
+      </c>
+      <c r="H12" s="2">
+        <v>1</v>
+      </c>
+      <c r="I12" s="2">
+        <v>5</v>
+      </c>
+      <c r="J12" s="2">
+        <v>0</v>
+      </c>
+      <c r="K12" s="2">
+        <v>0</v>
+      </c>
+      <c r="L12" s="2">
+        <v>6</v>
+      </c>
+      <c r="M12" s="2">
+        <v>0</v>
+      </c>
+      <c r="N12" s="2">
+        <v>0</v>
+      </c>
+      <c r="O12" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="P12" s="8" t="s">
+        <v>63</v>
+      </c>
+      <c r="Q12" s="8" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="13" s="2" customFormat="1" ht="27" customHeight="1" spans="1:17">
+      <c r="A13" s="2">
+        <v>32</v>
+      </c>
+      <c r="B13" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="C13" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="D13" s="2">
+        <v>2</v>
+      </c>
+      <c r="E13" s="2">
+        <v>3</v>
+      </c>
+      <c r="F13" s="2">
+        <v>2</v>
+      </c>
+      <c r="G13" s="2">
+        <v>6</v>
+      </c>
+      <c r="H13" s="2">
+        <v>0</v>
+      </c>
+      <c r="I13" s="2">
+        <v>5</v>
+      </c>
+      <c r="J13" s="2">
+        <v>0</v>
+      </c>
+      <c r="K13" s="2">
+        <v>0</v>
+      </c>
+      <c r="L13" s="2">
+        <v>8</v>
+      </c>
+      <c r="M13" s="2">
+        <v>3</v>
+      </c>
+      <c r="N13" s="2">
+        <v>0</v>
+      </c>
+      <c r="O13" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="P13" s="8" t="s">
+        <v>66</v>
+      </c>
+      <c r="Q13" s="8" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="14" s="4" customFormat="1" ht="27" customHeight="1" spans="1:17">
+      <c r="A14" s="4">
         <v>101</v>
       </c>
-      <c r="B11" s="4" t="s">
+      <c r="B14" s="4" t="s">
+        <v>68</v>
+      </c>
+      <c r="C14" s="4" t="s">
+        <v>38</v>
+      </c>
+      <c r="D14" s="4">
+        <v>1</v>
+      </c>
+      <c r="E14" s="4">
+        <v>0</v>
+      </c>
+      <c r="F14" s="4">
+        <v>2</v>
+      </c>
+      <c r="G14" s="4">
+        <v>0</v>
+      </c>
+      <c r="H14" s="4">
+        <v>0</v>
+      </c>
+      <c r="I14" s="4">
+        <v>3</v>
+      </c>
+      <c r="J14" s="4">
+        <v>0</v>
+      </c>
+      <c r="K14" s="4">
+        <v>1</v>
+      </c>
+      <c r="L14" s="4">
+        <v>12</v>
+      </c>
+      <c r="M14" s="4">
+        <v>0</v>
+      </c>
+      <c r="N14" s="4">
+        <v>0</v>
+      </c>
+      <c r="O14" s="4" t="s">
+        <v>69</v>
+      </c>
+      <c r="P14" s="10" t="s">
+        <v>70</v>
+      </c>
+      <c r="Q14" s="10">
+        <v>0.075</v>
+      </c>
+    </row>
+    <row r="15" s="4" customFormat="1" ht="30" customHeight="1" spans="1:17">
+      <c r="A15" s="4">
+        <v>102</v>
+      </c>
+      <c r="B15" s="4" t="s">
+        <v>71</v>
+      </c>
+      <c r="C15" s="4" t="s">
         <v>49</v>
       </c>
-      <c r="C11" s="4" t="s">
-        <v>38</v>
-      </c>
-      <c r="D11" s="4">
-        <v>1</v>
-      </c>
-      <c r="E11" s="4">
-        <v>0</v>
-      </c>
-      <c r="F11" s="4">
+      <c r="D15" s="4">
+        <v>1</v>
+      </c>
+      <c r="E15" s="4">
+        <v>0</v>
+      </c>
+      <c r="F15" s="4">
         <v>2</v>
       </c>
-      <c r="G11" s="4">
-        <v>0</v>
-      </c>
-      <c r="H11" s="4">
-        <v>0</v>
-      </c>
-      <c r="I11" s="4">
+      <c r="G15" s="4">
+        <v>0</v>
+      </c>
+      <c r="H15" s="4">
+        <v>0</v>
+      </c>
+      <c r="I15" s="4">
         <v>3</v>
       </c>
-      <c r="J11" s="4">
-        <v>0</v>
-      </c>
-      <c r="K11" s="4">
-        <v>1</v>
-      </c>
-      <c r="L11" s="4">
+      <c r="J15" s="4">
+        <v>0</v>
+      </c>
+      <c r="K15" s="4">
+        <v>1</v>
+      </c>
+      <c r="L15" s="4">
         <v>12</v>
       </c>
-      <c r="M11" s="4">
-        <v>0</v>
-      </c>
-      <c r="N11" s="4">
-        <v>0</v>
-      </c>
-      <c r="O11" s="4" t="s">
-        <v>50</v>
-      </c>
-      <c r="P11" s="10">
-        <v>20001</v>
-      </c>
-      <c r="Q11" s="4">
-        <v>0.075</v>
-      </c>
-    </row>
-    <row r="12" s="4" customFormat="1" ht="30" customHeight="1" spans="1:17">
-      <c r="A12" s="4">
-        <v>102</v>
-      </c>
-      <c r="B12" s="4" t="s">
-        <v>51</v>
-      </c>
-      <c r="C12" s="4" t="s">
-        <v>46</v>
-      </c>
-      <c r="D12" s="4">
-        <v>1</v>
-      </c>
-      <c r="E12" s="4">
-        <v>0</v>
-      </c>
-      <c r="F12" s="4">
-        <v>2</v>
-      </c>
-      <c r="G12" s="4">
-        <v>0</v>
-      </c>
-      <c r="H12" s="4">
-        <v>0</v>
-      </c>
-      <c r="I12" s="4">
-        <v>3</v>
-      </c>
-      <c r="J12" s="4">
-        <v>0</v>
-      </c>
-      <c r="K12" s="4">
-        <v>1</v>
-      </c>
-      <c r="L12" s="4">
-        <v>12</v>
-      </c>
-      <c r="M12" s="4">
-        <v>0</v>
-      </c>
-      <c r="N12" s="4">
-        <v>0</v>
-      </c>
-      <c r="O12" s="4" t="s">
-        <v>50</v>
-      </c>
-      <c r="P12" s="10">
-        <v>20001</v>
-      </c>
-      <c r="Q12" s="4">
+      <c r="M15" s="4">
+        <v>0</v>
+      </c>
+      <c r="N15" s="4">
+        <v>0</v>
+      </c>
+      <c r="O15" s="4" t="s">
+        <v>69</v>
+      </c>
+      <c r="P15" s="10" t="s">
+        <v>72</v>
+      </c>
+      <c r="Q15" s="10">
         <v>0.08</v>
       </c>
     </row>

--- a/Assets/Excel/技能配置表.xlsx
+++ b/Assets/Excel/技能配置表.xlsx
@@ -1904,7 +1904,7 @@
         <v>2</v>
       </c>
       <c r="G13" s="2">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="H13" s="2">
         <v>0</v>

--- a/Assets/Excel/技能配置表.xlsx
+++ b/Assets/Excel/技能配置表.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="103" uniqueCount="73">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="123" uniqueCount="85">
   <si>
     <t>f_id</t>
   </si>
@@ -255,6 +255,9 @@
     <t>牧师战技</t>
   </si>
   <si>
+    <t>恢复目标一定生命值</t>
+  </si>
+  <si>
     <t>311</t>
   </si>
   <si>
@@ -283,6 +286,39 @@
   </si>
   <si>
     <t>1021</t>
+  </si>
+  <si>
+    <t>霜陨</t>
+  </si>
+  <si>
+    <t>0.35,1.0625,1.775,2.4875,3.20</t>
+  </si>
+  <si>
+    <t>烬陨</t>
+  </si>
+  <si>
+    <t>1041</t>
+  </si>
+  <si>
+    <t>1.02</t>
+  </si>
+  <si>
+    <t>深渊之赐</t>
+  </si>
+  <si>
+    <t>为目标施加【渊涌】效果</t>
+  </si>
+  <si>
+    <t>1051</t>
+  </si>
+  <si>
+    <t>1</t>
+  </si>
+  <si>
+    <t>渊禁</t>
+  </si>
+  <si>
+    <t>创建术阵，使敌方全体添加【恐惧】效果，不可解除</t>
   </si>
 </sst>
 </file>
@@ -922,7 +958,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -938,19 +974,31 @@
     <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="49" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="49" fontId="0" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="0" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
@@ -1272,12 +1320,12 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:Q15"/>
+  <dimension ref="A1:Q19"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col min="1" max="1" width="14.875" customWidth="1"/>
     <col min="2" max="2" width="20.875" customWidth="1"/>
-    <col min="3" max="3" width="29.25" customWidth="1"/>
+    <col min="3" max="3" width="29.25" style="5" customWidth="1"/>
     <col min="4" max="4" width="22.875" customWidth="1"/>
     <col min="5" max="5" width="12.625" customWidth="1"/>
     <col min="6" max="6" width="24.375" customWidth="1"/>
@@ -1290,8 +1338,8 @@
     <col min="13" max="13" width="16" customWidth="1"/>
     <col min="14" max="14" width="14.625" customWidth="1"/>
     <col min="15" max="15" width="16" customWidth="1"/>
-    <col min="16" max="16" width="20.1083333333333" style="5" customWidth="1"/>
-    <col min="17" max="17" width="25.3166666666667" style="5" customWidth="1"/>
+    <col min="16" max="16" width="20.1083333333333" style="6" customWidth="1"/>
+    <col min="17" max="17" width="25.3166666666667" style="6" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" s="1" customFormat="1" ht="27" customHeight="1" spans="1:17">
@@ -1301,7 +1349,7 @@
       <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C1" s="7" t="s">
         <v>2</v>
       </c>
       <c r="D1" s="1" t="s">
@@ -1340,10 +1388,10 @@
       <c r="O1" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="P1" s="6" t="s">
+      <c r="P1" s="8" t="s">
         <v>15</v>
       </c>
-      <c r="Q1" s="6" t="s">
+      <c r="Q1" s="8" t="s">
         <v>16</v>
       </c>
     </row>
@@ -1354,7 +1402,7 @@
       <c r="B2" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="C2" s="1" t="s">
+      <c r="C2" s="7" t="s">
         <v>18</v>
       </c>
       <c r="D2" s="1" t="s">
@@ -1393,10 +1441,10 @@
       <c r="O2" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="P2" s="6" t="s">
+      <c r="P2" s="8" t="s">
         <v>18</v>
       </c>
-      <c r="Q2" s="6" t="s">
+      <c r="Q2" s="8" t="s">
         <v>18</v>
       </c>
     </row>
@@ -1404,8 +1452,9 @@
       <c r="A3" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="P3" s="6"/>
-      <c r="Q3" s="6"/>
+      <c r="C3" s="7"/>
+      <c r="P3" s="8"/>
+      <c r="Q3" s="8"/>
     </row>
     <row r="4" s="1" customFormat="1" ht="94.5" spans="1:17">
       <c r="A4" s="1" t="s">
@@ -1414,7 +1463,7 @@
       <c r="B4" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="C4" s="1" t="s">
+      <c r="C4" s="7" t="s">
         <v>22</v>
       </c>
       <c r="D4" s="7" t="s">
@@ -1453,10 +1502,10 @@
       <c r="O4" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="P4" s="6" t="s">
+      <c r="P4" s="8" t="s">
         <v>35</v>
       </c>
-      <c r="Q4" s="6" t="s">
+      <c r="Q4" s="8" t="s">
         <v>36</v>
       </c>
     </row>
@@ -1467,7 +1516,7 @@
       <c r="B5" s="2" t="s">
         <v>37</v>
       </c>
-      <c r="C5" s="2" t="s">
+      <c r="C5" s="9" t="s">
         <v>38</v>
       </c>
       <c r="D5" s="2">
@@ -1506,10 +1555,10 @@
       <c r="O5" s="2" t="s">
         <v>39</v>
       </c>
-      <c r="P5" s="8" t="s">
+      <c r="P5" s="10" t="s">
         <v>40</v>
       </c>
-      <c r="Q5" s="8">
+      <c r="Q5" s="10">
         <v>0.2</v>
       </c>
     </row>
@@ -1520,7 +1569,7 @@
       <c r="B6" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="C6" s="2" t="s">
+      <c r="C6" s="9" t="s">
         <v>38</v>
       </c>
       <c r="D6" s="2">
@@ -1559,10 +1608,10 @@
       <c r="O6" s="2" t="s">
         <v>42</v>
       </c>
-      <c r="P6" s="8" t="s">
+      <c r="P6" s="10" t="s">
         <v>43</v>
       </c>
-      <c r="Q6" s="8">
+      <c r="Q6" s="10">
         <v>0.1</v>
       </c>
     </row>
@@ -1573,7 +1622,7 @@
       <c r="B7" s="2" t="s">
         <v>44</v>
       </c>
-      <c r="C7" s="2" t="s">
+      <c r="C7" s="9" t="s">
         <v>38</v>
       </c>
       <c r="D7" s="2">
@@ -1612,10 +1661,10 @@
       <c r="O7" s="2" t="s">
         <v>45</v>
       </c>
-      <c r="P7" s="8" t="s">
+      <c r="P7" s="10" t="s">
         <v>46</v>
       </c>
-      <c r="Q7" s="8" t="s">
+      <c r="Q7" s="10" t="s">
         <v>47</v>
       </c>
     </row>
@@ -1626,7 +1675,7 @@
       <c r="B8" s="3" t="s">
         <v>48</v>
       </c>
-      <c r="C8" s="3" t="s">
+      <c r="C8" s="11" t="s">
         <v>49</v>
       </c>
       <c r="D8" s="3">
@@ -1665,10 +1714,10 @@
       <c r="O8" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="P8" s="9" t="s">
+      <c r="P8" s="12" t="s">
         <v>50</v>
       </c>
-      <c r="Q8" s="9" t="s">
+      <c r="Q8" s="12" t="s">
         <v>51</v>
       </c>
     </row>
@@ -1679,7 +1728,7 @@
       <c r="B9" s="3" t="s">
         <v>52</v>
       </c>
-      <c r="C9" s="3" t="s">
+      <c r="C9" s="11" t="s">
         <v>49</v>
       </c>
       <c r="D9" s="3">
@@ -1718,10 +1767,10 @@
       <c r="O9" s="3" t="s">
         <v>42</v>
       </c>
-      <c r="P9" s="9" t="s">
+      <c r="P9" s="12" t="s">
         <v>53</v>
       </c>
-      <c r="Q9" s="9" t="s">
+      <c r="Q9" s="12" t="s">
         <v>54</v>
       </c>
     </row>
@@ -1732,7 +1781,7 @@
       <c r="B10" s="3" t="s">
         <v>55</v>
       </c>
-      <c r="C10" s="3" t="s">
+      <c r="C10" s="11" t="s">
         <v>49</v>
       </c>
       <c r="D10" s="3">
@@ -1771,10 +1820,10 @@
       <c r="O10" s="3" t="s">
         <v>45</v>
       </c>
-      <c r="P10" s="9" t="s">
+      <c r="P10" s="12" t="s">
         <v>56</v>
       </c>
-      <c r="Q10" s="9" t="s">
+      <c r="Q10" s="12" t="s">
         <v>57</v>
       </c>
     </row>
@@ -1785,7 +1834,7 @@
       <c r="B11" s="2" t="s">
         <v>58</v>
       </c>
-      <c r="C11" s="2" t="s">
+      <c r="C11" s="9" t="s">
         <v>59</v>
       </c>
       <c r="D11" s="2">
@@ -1824,10 +1873,10 @@
       <c r="O11" s="2" t="s">
         <v>39</v>
       </c>
-      <c r="P11" s="8" t="s">
+      <c r="P11" s="10" t="s">
         <v>60</v>
       </c>
-      <c r="Q11" s="8" t="s">
+      <c r="Q11" s="10" t="s">
         <v>61</v>
       </c>
     </row>
@@ -1838,8 +1887,8 @@
       <c r="B12" s="2" t="s">
         <v>62</v>
       </c>
-      <c r="C12" s="2" t="s">
-        <v>59</v>
+      <c r="C12" s="9" t="s">
+        <v>63</v>
       </c>
       <c r="D12" s="2">
         <v>1</v>
@@ -1877,11 +1926,11 @@
       <c r="O12" s="2" t="s">
         <v>42</v>
       </c>
-      <c r="P12" s="8" t="s">
-        <v>63</v>
-      </c>
-      <c r="Q12" s="8" t="s">
+      <c r="P12" s="10" t="s">
         <v>64</v>
+      </c>
+      <c r="Q12" s="10" t="s">
+        <v>65</v>
       </c>
     </row>
     <row r="13" s="2" customFormat="1" ht="27" customHeight="1" spans="1:17">
@@ -1889,9 +1938,9 @@
         <v>32</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>65</v>
-      </c>
-      <c r="C13" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="C13" s="9" t="s">
         <v>59</v>
       </c>
       <c r="D13" s="2">
@@ -1930,11 +1979,11 @@
       <c r="O13" s="2" t="s">
         <v>45</v>
       </c>
-      <c r="P13" s="8" t="s">
-        <v>66</v>
-      </c>
-      <c r="Q13" s="8" t="s">
+      <c r="P13" s="10" t="s">
         <v>67</v>
+      </c>
+      <c r="Q13" s="10" t="s">
+        <v>68</v>
       </c>
     </row>
     <row r="14" s="4" customFormat="1" ht="27" customHeight="1" spans="1:17">
@@ -1942,9 +1991,9 @@
         <v>101</v>
       </c>
       <c r="B14" s="4" t="s">
-        <v>68</v>
-      </c>
-      <c r="C14" s="4" t="s">
+        <v>69</v>
+      </c>
+      <c r="C14" s="13" t="s">
         <v>38</v>
       </c>
       <c r="D14" s="4">
@@ -1963,7 +2012,7 @@
         <v>0</v>
       </c>
       <c r="I14" s="4">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="J14" s="4">
         <v>0</v>
@@ -1981,66 +2030,278 @@
         <v>0</v>
       </c>
       <c r="O14" s="4" t="s">
-        <v>69</v>
-      </c>
-      <c r="P14" s="10" t="s">
         <v>70</v>
       </c>
-      <c r="Q14" s="10">
+      <c r="P14" s="14" t="s">
+        <v>71</v>
+      </c>
+      <c r="Q14" s="14">
         <v>0.075</v>
       </c>
     </row>
-    <row r="15" s="4" customFormat="1" ht="30" customHeight="1" spans="1:17">
-      <c r="A15" s="4">
+    <row r="15" s="3" customFormat="1" ht="30" customHeight="1" spans="1:17">
+      <c r="A15" s="3">
         <v>102</v>
       </c>
-      <c r="B15" s="4" t="s">
+      <c r="B15" s="3" t="s">
+        <v>72</v>
+      </c>
+      <c r="C15" s="11" t="s">
+        <v>49</v>
+      </c>
+      <c r="D15" s="3">
+        <v>1</v>
+      </c>
+      <c r="E15" s="3">
+        <v>0</v>
+      </c>
+      <c r="F15" s="3">
+        <v>2</v>
+      </c>
+      <c r="G15" s="3">
+        <v>0</v>
+      </c>
+      <c r="H15" s="3">
+        <v>0</v>
+      </c>
+      <c r="I15" s="3">
+        <v>2</v>
+      </c>
+      <c r="J15" s="3">
+        <v>0</v>
+      </c>
+      <c r="K15" s="3">
+        <v>1</v>
+      </c>
+      <c r="L15" s="3">
+        <v>12</v>
+      </c>
+      <c r="M15" s="3">
+        <v>0</v>
+      </c>
+      <c r="N15" s="3">
+        <v>0</v>
+      </c>
+      <c r="O15" s="3" t="s">
+        <v>70</v>
+      </c>
+      <c r="P15" s="12" t="s">
+        <v>73</v>
+      </c>
+      <c r="Q15" s="12">
+        <v>0.08</v>
+      </c>
+    </row>
+    <row r="16" s="4" customFormat="1" ht="36" customHeight="1" spans="1:17">
+      <c r="A16" s="4">
+        <v>103</v>
+      </c>
+      <c r="B16" s="4" t="s">
+        <v>74</v>
+      </c>
+      <c r="C16" s="13" t="s">
+        <v>49</v>
+      </c>
+      <c r="D16" s="4">
+        <v>3</v>
+      </c>
+      <c r="E16" s="4">
+        <v>0</v>
+      </c>
+      <c r="F16" s="4">
+        <v>2</v>
+      </c>
+      <c r="G16" s="4">
+        <v>0</v>
+      </c>
+      <c r="H16" s="4">
+        <v>0</v>
+      </c>
+      <c r="I16" s="4">
+        <v>2</v>
+      </c>
+      <c r="J16" s="4">
+        <v>0</v>
+      </c>
+      <c r="K16" s="4">
+        <v>1</v>
+      </c>
+      <c r="L16" s="4">
+        <v>12</v>
+      </c>
+      <c r="M16" s="4">
+        <v>0</v>
+      </c>
+      <c r="N16" s="4">
+        <v>0</v>
+      </c>
+      <c r="O16" s="4" t="s">
+        <v>70</v>
+      </c>
+      <c r="P16" s="14" t="s">
         <v>71</v>
       </c>
-      <c r="C15" s="4" t="s">
-        <v>49</v>
-      </c>
-      <c r="D15" s="4">
-        <v>1</v>
-      </c>
-      <c r="E15" s="4">
-        <v>0</v>
-      </c>
-      <c r="F15" s="4">
-        <v>2</v>
-      </c>
-      <c r="G15" s="4">
-        <v>0</v>
-      </c>
-      <c r="H15" s="4">
-        <v>0</v>
-      </c>
-      <c r="I15" s="4">
+      <c r="Q16" s="14" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="17" s="4" customFormat="1" ht="36" customHeight="1" spans="1:17">
+      <c r="A17" s="4">
+        <v>104</v>
+      </c>
+      <c r="B17" s="4" t="s">
+        <v>76</v>
+      </c>
+      <c r="C17" s="13" t="s">
+        <v>38</v>
+      </c>
+      <c r="D17" s="4">
+        <v>2</v>
+      </c>
+      <c r="E17" s="4">
+        <v>0</v>
+      </c>
+      <c r="F17" s="4">
+        <v>2</v>
+      </c>
+      <c r="G17" s="4">
+        <v>0</v>
+      </c>
+      <c r="H17" s="4">
+        <v>0</v>
+      </c>
+      <c r="I17" s="4">
+        <v>1</v>
+      </c>
+      <c r="J17" s="4">
+        <v>0</v>
+      </c>
+      <c r="K17" s="4">
+        <v>1</v>
+      </c>
+      <c r="L17" s="4">
+        <v>12</v>
+      </c>
+      <c r="M17" s="4">
+        <v>0</v>
+      </c>
+      <c r="N17" s="4">
+        <v>0</v>
+      </c>
+      <c r="O17" s="4" t="s">
+        <v>70</v>
+      </c>
+      <c r="P17" s="14" t="s">
+        <v>77</v>
+      </c>
+      <c r="Q17" s="14" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="18" s="4" customFormat="1" ht="37" customHeight="1" spans="1:17">
+      <c r="A18" s="4">
+        <v>105</v>
+      </c>
+      <c r="B18" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="C18" s="13" t="s">
+        <v>80</v>
+      </c>
+      <c r="D18" s="4">
+        <v>1</v>
+      </c>
+      <c r="E18" s="4">
+        <v>0</v>
+      </c>
+      <c r="F18" s="4">
+        <v>1</v>
+      </c>
+      <c r="G18" s="4">
+        <v>0</v>
+      </c>
+      <c r="H18" s="4">
+        <v>0</v>
+      </c>
+      <c r="I18" s="4">
+        <v>0</v>
+      </c>
+      <c r="J18" s="4">
+        <v>0</v>
+      </c>
+      <c r="K18" s="4">
+        <v>1</v>
+      </c>
+      <c r="L18" s="4">
+        <v>12</v>
+      </c>
+      <c r="M18" s="4">
+        <v>0</v>
+      </c>
+      <c r="N18" s="4">
+        <v>0</v>
+      </c>
+      <c r="O18" s="4" t="s">
+        <v>70</v>
+      </c>
+      <c r="P18" s="14" t="s">
+        <v>81</v>
+      </c>
+      <c r="Q18" s="14" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="19" s="4" customFormat="1" ht="37" customHeight="1" spans="1:17">
+      <c r="A19" s="4">
+        <v>106</v>
+      </c>
+      <c r="B19" s="4" t="s">
+        <v>83</v>
+      </c>
+      <c r="C19" s="13" t="s">
+        <v>84</v>
+      </c>
+      <c r="D19" s="4">
         <v>3</v>
       </c>
-      <c r="J15" s="4">
-        <v>0</v>
-      </c>
-      <c r="K15" s="4">
-        <v>1</v>
-      </c>
-      <c r="L15" s="4">
+      <c r="E19" s="4">
+        <v>0</v>
+      </c>
+      <c r="F19" s="4">
+        <v>2</v>
+      </c>
+      <c r="G19" s="4">
+        <v>0</v>
+      </c>
+      <c r="H19" s="4">
+        <v>0</v>
+      </c>
+      <c r="I19" s="4">
+        <v>0</v>
+      </c>
+      <c r="J19" s="4">
+        <v>0</v>
+      </c>
+      <c r="K19" s="4">
+        <v>1</v>
+      </c>
+      <c r="L19" s="4">
         <v>12</v>
       </c>
-      <c r="M15" s="4">
-        <v>0</v>
-      </c>
-      <c r="N15" s="4">
-        <v>0</v>
-      </c>
-      <c r="O15" s="4" t="s">
-        <v>69</v>
-      </c>
-      <c r="P15" s="10" t="s">
-        <v>72</v>
-      </c>
-      <c r="Q15" s="10">
-        <v>0.08</v>
+      <c r="M19" s="4">
+        <v>0</v>
+      </c>
+      <c r="N19" s="4">
+        <v>0</v>
+      </c>
+      <c r="O19" s="4" t="s">
+        <v>70</v>
+      </c>
+      <c r="P19" s="14" t="s">
+        <v>50</v>
+      </c>
+      <c r="Q19" s="14" t="s">
+        <v>82</v>
       </c>
     </row>
   </sheetData>

--- a/Assets/Excel/技能配置表.xlsx
+++ b/Assets/Excel/技能配置表.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="123" uniqueCount="85">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="123" uniqueCount="87">
   <si>
     <t>f_id</t>
   </si>
@@ -183,7 +183,7 @@
     <t>造成100%攻击力的火属性伤害</t>
   </si>
   <si>
-    <t>NormalAttack</t>
+    <t>Skill Layer.NormalAttack</t>
   </si>
   <si>
     <t>101</t>
@@ -192,7 +192,7 @@
     <t>战士战技</t>
   </si>
   <si>
-    <t>BattleAttack</t>
+    <t>Skill Layer.BattleAttack</t>
   </si>
   <si>
     <t>111</t>
@@ -201,7 +201,7 @@
     <t>战士终结技</t>
   </si>
   <si>
-    <t>UltimateAttack</t>
+    <t>Skill Layer.UltimateAttack</t>
   </si>
   <si>
     <t>121</t>
@@ -276,7 +276,7 @@
     <t>史莱姆攻击</t>
   </si>
   <si>
-    <t>Attack</t>
+    <t>Skill Layer.Attack</t>
   </si>
   <si>
     <t>1011</t>
@@ -291,10 +291,16 @@
     <t>霜陨</t>
   </si>
   <si>
+    <t>Skill Layer.Attack02</t>
+  </si>
+  <si>
     <t>0.35,1.0625,1.775,2.4875,3.20</t>
   </si>
   <si>
     <t>烬陨</t>
+  </si>
+  <si>
+    <t>Skill Layer.Attack01</t>
   </si>
   <si>
     <t>1041</t>
@@ -1337,7 +1343,7 @@
     <col min="12" max="12" width="32.8166666666667" customWidth="1"/>
     <col min="13" max="13" width="16" customWidth="1"/>
     <col min="14" max="14" width="14.625" customWidth="1"/>
-    <col min="15" max="15" width="16" customWidth="1"/>
+    <col min="15" max="15" width="27.125" customWidth="1"/>
     <col min="16" max="16" width="20.1083333333333" style="6" customWidth="1"/>
     <col min="17" max="17" width="25.3166666666667" style="6" customWidth="1"/>
   </cols>
@@ -2136,13 +2142,13 @@
         <v>0</v>
       </c>
       <c r="O16" s="4" t="s">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="P16" s="14" t="s">
         <v>71</v>
       </c>
       <c r="Q16" s="14" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
     </row>
     <row r="17" s="4" customFormat="1" ht="36" customHeight="1" spans="1:17">
@@ -2150,7 +2156,7 @@
         <v>104</v>
       </c>
       <c r="B17" s="4" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="C17" s="13" t="s">
         <v>38</v>
@@ -2189,13 +2195,13 @@
         <v>0</v>
       </c>
       <c r="O17" s="4" t="s">
-        <v>70</v>
+        <v>78</v>
       </c>
       <c r="P17" s="14" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="Q17" s="14" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
     </row>
     <row r="18" s="4" customFormat="1" ht="37" customHeight="1" spans="1:17">
@@ -2203,10 +2209,10 @@
         <v>105</v>
       </c>
       <c r="B18" s="4" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="C18" s="13" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="D18" s="4">
         <v>1</v>
@@ -2242,13 +2248,13 @@
         <v>0</v>
       </c>
       <c r="O18" s="4" t="s">
-        <v>70</v>
+        <v>78</v>
       </c>
       <c r="P18" s="14" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="Q18" s="14" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
     </row>
     <row r="19" s="4" customFormat="1" ht="37" customHeight="1" spans="1:17">
@@ -2256,10 +2262,10 @@
         <v>106</v>
       </c>
       <c r="B19" s="4" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="C19" s="13" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="D19" s="4">
         <v>3</v>
@@ -2295,13 +2301,13 @@
         <v>0</v>
       </c>
       <c r="O19" s="4" t="s">
-        <v>70</v>
+        <v>78</v>
       </c>
       <c r="P19" s="14" t="s">
         <v>50</v>
       </c>
       <c r="Q19" s="14" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
     </row>
   </sheetData>

--- a/Assets/Excel/技能配置表.xlsx
+++ b/Assets/Excel/技能配置表.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="123" uniqueCount="87">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="123" uniqueCount="89">
   <si>
     <t>f_id</t>
   </si>
@@ -71,7 +71,7 @@
     <t>f_priority</t>
   </si>
   <si>
-    <t>f_animName</t>
+    <t>f_animNames</t>
   </si>
   <si>
     <t>f_statusId</t>
@@ -168,7 +168,7 @@
 数值越大越高</t>
   </si>
   <si>
-    <t>动画名称</t>
+    <t>动画名称数组</t>
   </si>
   <si>
     <t>技能Buff效果ID</t>
@@ -183,39 +183,42 @@
     <t>造成100%攻击力的火属性伤害</t>
   </si>
   <si>
+    <t>Skill Layer.NormalAttack.Roll，Skill Layer.NormalAttack.AttackAfterRoll</t>
+  </si>
+  <si>
+    <t>101</t>
+  </si>
+  <si>
+    <t>战士战技</t>
+  </si>
+  <si>
+    <t>Skill Layer.BattleAttack</t>
+  </si>
+  <si>
+    <t>111</t>
+  </si>
+  <si>
+    <t>战士终结技</t>
+  </si>
+  <si>
+    <t>Skill Layer.UltimateAttack</t>
+  </si>
+  <si>
+    <t>121</t>
+  </si>
+  <si>
+    <t>0.16,0.39,0.58,0.64,0.79,0.81</t>
+  </si>
+  <si>
+    <t>法师普攻</t>
+  </si>
+  <si>
+    <t>造成100%攻击力的冰属性伤害</t>
+  </si>
+  <si>
     <t>Skill Layer.NormalAttack</t>
   </si>
   <si>
-    <t>101</t>
-  </si>
-  <si>
-    <t>战士战技</t>
-  </si>
-  <si>
-    <t>Skill Layer.BattleAttack</t>
-  </si>
-  <si>
-    <t>111</t>
-  </si>
-  <si>
-    <t>战士终结技</t>
-  </si>
-  <si>
-    <t>Skill Layer.UltimateAttack</t>
-  </si>
-  <si>
-    <t>121</t>
-  </si>
-  <si>
-    <t>0.16,0.39,0.58,0.64,0.79,0.81</t>
-  </si>
-  <si>
-    <t>法师普攻</t>
-  </si>
-  <si>
-    <t>造成100%攻击力的冰属性伤害</t>
-  </si>
-  <si>
     <t>201</t>
   </si>
   <si>
@@ -265,6 +268,9 @@
   </si>
   <si>
     <t>牧师终结技</t>
+  </si>
+  <si>
+    <t>Skill Layer.UltimateAttack.Priest_Ultimate_01,Skill Layer.UltimateAttack.Priest_Ultimate_02</t>
   </si>
   <si>
     <t>321</t>
@@ -1343,7 +1349,7 @@
     <col min="12" max="12" width="32.8166666666667" customWidth="1"/>
     <col min="13" max="13" width="16" customWidth="1"/>
     <col min="14" max="14" width="14.625" customWidth="1"/>
-    <col min="15" max="15" width="27.125" customWidth="1"/>
+    <col min="15" max="15" width="50.375" customWidth="1"/>
     <col min="16" max="16" width="20.1083333333333" style="6" customWidth="1"/>
     <col min="17" max="17" width="25.3166666666667" style="6" customWidth="1"/>
   </cols>
@@ -1558,7 +1564,7 @@
       <c r="N5" s="2">
         <v>0</v>
       </c>
-      <c r="O5" s="2" t="s">
+      <c r="O5" s="9" t="s">
         <v>39</v>
       </c>
       <c r="P5" s="10" t="s">
@@ -1718,13 +1724,13 @@
         <v>0</v>
       </c>
       <c r="O8" s="3" t="s">
-        <v>39</v>
+        <v>50</v>
       </c>
       <c r="P8" s="12" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="Q8" s="12" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
     </row>
     <row r="9" s="3" customFormat="1" ht="35" customHeight="1" spans="1:17">
@@ -1732,7 +1738,7 @@
         <v>21</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="C9" s="11" t="s">
         <v>49</v>
@@ -1774,10 +1780,10 @@
         <v>42</v>
       </c>
       <c r="P9" s="12" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="Q9" s="12" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
     </row>
     <row r="10" s="3" customFormat="1" ht="35" customHeight="1" spans="1:17">
@@ -1785,7 +1791,7 @@
         <v>22</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="C10" s="11" t="s">
         <v>49</v>
@@ -1827,10 +1833,10 @@
         <v>45</v>
       </c>
       <c r="P10" s="12" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="Q10" s="12" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
     </row>
     <row r="11" s="2" customFormat="1" ht="27" customHeight="1" spans="1:17">
@@ -1838,10 +1844,10 @@
         <v>30</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="C11" s="9" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="D11" s="2">
         <v>1</v>
@@ -1877,13 +1883,13 @@
         <v>0</v>
       </c>
       <c r="O11" s="2" t="s">
-        <v>39</v>
+        <v>50</v>
       </c>
       <c r="P11" s="10" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="Q11" s="10" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
     </row>
     <row r="12" s="2" customFormat="1" ht="27" customHeight="1" spans="1:17">
@@ -1891,10 +1897,10 @@
         <v>31</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="C12" s="9" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="D12" s="2">
         <v>1</v>
@@ -1933,21 +1939,21 @@
         <v>42</v>
       </c>
       <c r="P12" s="10" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="Q12" s="10" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
     </row>
-    <row r="13" s="2" customFormat="1" ht="27" customHeight="1" spans="1:17">
+    <row r="13" s="2" customFormat="1" ht="40.5" spans="1:17">
       <c r="A13" s="2">
         <v>32</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="C13" s="9" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="D13" s="2">
         <v>2</v>
@@ -1982,22 +1988,22 @@
       <c r="N13" s="2">
         <v>0</v>
       </c>
-      <c r="O13" s="2" t="s">
-        <v>45</v>
+      <c r="O13" s="9" t="s">
+        <v>68</v>
       </c>
       <c r="P13" s="10" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="Q13" s="10" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
     </row>
-    <row r="14" s="4" customFormat="1" ht="27" customHeight="1" spans="1:17">
+    <row r="14" s="4" customFormat="1" ht="35" customHeight="1" spans="1:17">
       <c r="A14" s="4">
         <v>101</v>
       </c>
       <c r="B14" s="4" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="C14" s="13" t="s">
         <v>38</v>
@@ -2036,10 +2042,10 @@
         <v>0</v>
       </c>
       <c r="O14" s="4" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="P14" s="14" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="Q14" s="14">
         <v>0.075</v>
@@ -2050,7 +2056,7 @@
         <v>102</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="C15" s="11" t="s">
         <v>49</v>
@@ -2089,10 +2095,10 @@
         <v>0</v>
       </c>
       <c r="O15" s="3" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="P15" s="12" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="Q15" s="12">
         <v>0.08</v>
@@ -2103,7 +2109,7 @@
         <v>103</v>
       </c>
       <c r="B16" s="4" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="C16" s="13" t="s">
         <v>49</v>
@@ -2142,13 +2148,13 @@
         <v>0</v>
       </c>
       <c r="O16" s="4" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="P16" s="14" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="Q16" s="14" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
     </row>
     <row r="17" s="4" customFormat="1" ht="36" customHeight="1" spans="1:17">
@@ -2156,7 +2162,7 @@
         <v>104</v>
       </c>
       <c r="B17" s="4" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="C17" s="13" t="s">
         <v>38</v>
@@ -2195,13 +2201,13 @@
         <v>0</v>
       </c>
       <c r="O17" s="4" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="P17" s="14" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="Q17" s="14" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
     </row>
     <row r="18" s="4" customFormat="1" ht="37" customHeight="1" spans="1:17">
@@ -2209,10 +2215,10 @@
         <v>105</v>
       </c>
       <c r="B18" s="4" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="C18" s="13" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="D18" s="4">
         <v>1</v>
@@ -2248,13 +2254,13 @@
         <v>0</v>
       </c>
       <c r="O18" s="4" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="P18" s="14" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="Q18" s="14" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
     </row>
     <row r="19" s="4" customFormat="1" ht="37" customHeight="1" spans="1:17">
@@ -2262,10 +2268,10 @@
         <v>106</v>
       </c>
       <c r="B19" s="4" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="C19" s="13" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="D19" s="4">
         <v>3</v>
@@ -2301,13 +2307,13 @@
         <v>0</v>
       </c>
       <c r="O19" s="4" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="P19" s="14" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="Q19" s="14" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
     </row>
   </sheetData>

--- a/Assets/Excel/技能配置表.xlsx
+++ b/Assets/Excel/技能配置表.xlsx
@@ -183,7 +183,7 @@
     <t>造成100%攻击力的火属性伤害</t>
   </si>
   <si>
-    <t>Skill Layer.NormalAttack.Roll，Skill Layer.NormalAttack.AttackAfterRoll</t>
+    <t>Battle Layer.NormalAttack.Roll，Battle Layer.NormalAttack.AttackAfterRoll</t>
   </si>
   <si>
     <t>101</t>
@@ -192,7 +192,7 @@
     <t>战士战技</t>
   </si>
   <si>
-    <t>Skill Layer.BattleAttack</t>
+    <t>Battle Layer.BattleAttack</t>
   </si>
   <si>
     <t>111</t>
@@ -201,7 +201,7 @@
     <t>战士终结技</t>
   </si>
   <si>
-    <t>Skill Layer.UltimateAttack</t>
+    <t>Battle Layer.UltimateAttack</t>
   </si>
   <si>
     <t>121</t>
@@ -216,7 +216,7 @@
     <t>造成100%攻击力的冰属性伤害</t>
   </si>
   <si>
-    <t>Skill Layer.NormalAttack</t>
+    <t>Battle Layer.NormalAttack</t>
   </si>
   <si>
     <t>201</t>
@@ -270,7 +270,7 @@
     <t>牧师终结技</t>
   </si>
   <si>
-    <t>Skill Layer.UltimateAttack.Priest_Ultimate_01,Skill Layer.UltimateAttack.Priest_Ultimate_02</t>
+    <t>Battle Layer.UltimateAttack.Priest_Ultimate_01,Battle Layer.UltimateAttack.Priest_Ultimate_02</t>
   </si>
   <si>
     <t>321</t>
@@ -282,7 +282,7 @@
     <t>史莱姆攻击</t>
   </si>
   <si>
-    <t>Skill Layer.Attack</t>
+    <t>Battle Layer.Attack</t>
   </si>
   <si>
     <t>1011</t>
@@ -297,7 +297,7 @@
     <t>霜陨</t>
   </si>
   <si>
-    <t>Skill Layer.Attack02</t>
+    <t>Battle Layer.Attack02</t>
   </si>
   <si>
     <t>0.35,1.0625,1.775,2.4875,3.20</t>
@@ -306,7 +306,7 @@
     <t>烬陨</t>
   </si>
   <si>
-    <t>Skill Layer.Attack01</t>
+    <t>Battle Layer.Attack01</t>
   </si>
   <si>
     <t>1041</t>
